--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_PhuKienRFID+VNSH03_260626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_PhuKienRFID+VNSH03_260626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3C70AA-A884-41B8-A907-5795E8C3E49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810C17DA-C8FD-406F-9BC9-FCA175A27ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -522,6 +522,12 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -587,12 +593,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1022,66 +1022,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="39" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="42" t="s">
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="43"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="45"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="44" t="s">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E11" s="21"/>
       <c r="F11" s="16"/>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="26" t="s">
         <v>34</v>
       </c>
       <c r="H11" s="20"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="E12" s="20"/>
       <c r="F12" s="16"/>
-      <c r="G12" s="25"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="16"/>
-      <c r="G13" s="25"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="16"/>
-      <c r="G14" s="25"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="20"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E15" s="20"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="25"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="16"/>
-      <c r="G16" s="25"/>
+      <c r="G16" s="27"/>
       <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:8" s="2" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E17" s="20"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="26"/>
+      <c r="G17" s="28"/>
       <c r="H17" s="23" t="s">
         <v>37</v>
       </c>
@@ -1318,40 +1318,40 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46" t="s">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46" t="s">
+      <c r="D20" s="24"/>
+      <c r="E20" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46" t="s">
+      <c r="F20" s="24"/>
+      <c r="G20" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H20" s="46"/>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47" t="s">
+      <c r="D21" s="25"/>
+      <c r="E21" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47" t="s">
+      <c r="F21" s="25"/>
+      <c r="G21" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="47"/>
+      <c r="H21" s="25"/>
     </row>
     <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12"/>
@@ -1404,22 +1404,22 @@
       <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46" t="s">
+      <c r="B27" s="24"/>
+      <c r="C27" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46" t="s">
+      <c r="D27" s="24"/>
+      <c r="E27" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46" t="s">
+      <c r="F27" s="24"/>
+      <c r="G27" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H27" s="46"/>
+      <c r="H27" s="24"/>
     </row>
     <row r="28" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="29" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1445,6 +1445,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G11:G17"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="C27:D27"/>
@@ -1457,13 +1464,6 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G11:G17"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
